--- a/RACP Data/2017_RACP.xlsx
+++ b/RACP Data/2017_RACP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pagov-my.sharepoint.com/personal/linnmiller_pa_gov/Documents/Desktop/RACP Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pagov-my.sharepoint.com/personal/linnmiller_pa_gov/Documents/Desktop/racp_sector_classifer/RACP Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="6" documentId="8_{5646A8DD-BBB4-4B4B-8845-7877353FC5CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8240DAE-7C81-4CFC-BD8E-B335EEA96E8C}"/>
   <bookViews>
-    <workbookView xWindow="1428" yWindow="1428" windowWidth="17280" windowHeight="8928" tabRatio="546" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="546" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RACP Awards 2017" sheetId="3" r:id="rId1"/>
@@ -6293,10 +6293,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6672,19 +6668,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{239F3628-AD58-49F9-9A76-FC08F8C89352}">
   <dimension ref="A1:I408"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="12.88671875" style="20" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="30.6640625" customWidth="1"/>
-    <col min="4" max="4" width="20.5546875" customWidth="1"/>
+    <col min="1" max="2" width="12.85546875" style="20" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="20.5703125" customWidth="1"/>
     <col min="5" max="5" width="22" style="20" customWidth="1"/>
-    <col min="6" max="6" width="17.33203125" customWidth="1"/>
-    <col min="7" max="7" width="15.44140625" customWidth="1"/>
-    <col min="8" max="8" width="15.44140625" style="21" customWidth="1"/>
-    <col min="9" max="9" width="50.5546875" customWidth="1"/>
+    <col min="6" max="6" width="17.28515625" customWidth="1"/>
+    <col min="7" max="7" width="15.42578125" customWidth="1"/>
+    <col min="8" max="8" width="15.42578125" style="21" customWidth="1"/>
+    <col min="9" max="9" width="50.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="24" t="s">
@@ -6697,7 +6693,7 @@
       <c r="H1" s="24"/>
       <c r="I1" s="24"/>
     </row>
-    <row r="2" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="25" t="s">
@@ -6710,7 +6706,7 @@
       <c r="H2" s="25"/>
       <c r="I2" s="25"/>
     </row>
-    <row r="3" spans="1:9" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="26" t="s">
@@ -6723,7 +6719,7 @@
       <c r="H3" s="26"/>
       <c r="I3" s="26"/>
     </row>
-    <row r="4" spans="1:9" ht="47.4" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="63.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
         <v>2</v>
       </c>
@@ -6752,7 +6748,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:9" s="12" customFormat="1" ht="105.6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" s="12" customFormat="1" ht="102" x14ac:dyDescent="0.2">
       <c r="A5" s="14" t="s">
         <v>10</v>
       </c>
@@ -6781,7 +6777,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="132" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>16</v>
       </c>
@@ -6810,7 +6806,7 @@
         <v>1783</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="303.60000000000002" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="306" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>19</v>
       </c>
@@ -6835,7 +6831,7 @@
         <v>1784</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="105.6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>22</v>
       </c>
@@ -6860,7 +6856,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:9" s="12" customFormat="1" ht="92.4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" s="12" customFormat="1" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>27</v>
       </c>
@@ -6889,7 +6885,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:9" s="12" customFormat="1" ht="66" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" s="12" customFormat="1" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>31</v>
       </c>
@@ -6914,7 +6910,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="277.2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" ht="267.75" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>35</v>
       </c>
@@ -6939,7 +6935,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="132" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
         <v>39</v>
       </c>
@@ -6964,7 +6960,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="145.19999999999999" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" ht="140.25" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
         <v>43</v>
       </c>
@@ -6993,7 +6989,7 @@
         <v>1791</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="105.6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
         <v>47</v>
       </c>
@@ -7022,7 +7018,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="118.8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
         <v>52</v>
       </c>
@@ -7051,7 +7047,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="118.8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
         <v>56</v>
       </c>
@@ -7080,7 +7076,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
         <v>60</v>
       </c>
@@ -7105,7 +7101,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="66" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
         <v>65</v>
       </c>
@@ -7130,7 +7126,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
         <v>68</v>
       </c>
@@ -7155,7 +7151,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
         <v>72</v>
       </c>
@@ -7184,7 +7180,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
         <v>76</v>
       </c>
@@ -7209,7 +7205,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="158.4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="153" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
         <v>80</v>
       </c>
@@ -7238,7 +7234,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="145.19999999999999" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" ht="153" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
         <v>84</v>
       </c>
@@ -7263,7 +7259,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="118.8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
         <v>88</v>
       </c>
@@ -7288,7 +7284,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="92.4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
         <v>92</v>
       </c>
@@ -7313,7 +7309,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
         <v>96</v>
       </c>
@@ -7342,7 +7338,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="92.4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" ht="102" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
         <v>101</v>
       </c>
@@ -7371,7 +7367,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
         <v>105</v>
       </c>
@@ -7396,7 +7392,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="105.6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
         <v>108</v>
       </c>
@@ -7421,7 +7417,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
         <v>112</v>
       </c>
@@ -7450,7 +7446,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
         <v>116</v>
       </c>
@@ -7475,7 +7471,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="211.2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" ht="216.75" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
         <v>120</v>
       </c>
@@ -7500,7 +7496,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
         <v>124</v>
       </c>
@@ -7529,7 +7525,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
         <v>129</v>
       </c>
@@ -7558,7 +7554,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="145.19999999999999" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" ht="140.25" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
         <v>134</v>
       </c>
@@ -7587,7 +7583,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
         <v>138</v>
       </c>
@@ -7616,7 +7612,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="66" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
         <v>141</v>
       </c>
@@ -7645,7 +7641,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="184.8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" ht="191.25" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
         <v>144</v>
       </c>
@@ -7670,7 +7666,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
         <v>149</v>
       </c>
@@ -7695,7 +7691,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
         <v>153</v>
       </c>
@@ -7720,7 +7716,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="66" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
         <v>158</v>
       </c>
@@ -7749,7 +7745,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="66" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
         <v>162</v>
       </c>
@@ -7778,7 +7774,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
         <v>166</v>
       </c>
@@ -7807,7 +7803,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
         <v>170</v>
       </c>
@@ -7832,7 +7828,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="105.6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" ht="102" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
         <v>174</v>
       </c>
@@ -7857,7 +7853,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="105.6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" ht="102" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
         <v>177</v>
       </c>
@@ -7886,7 +7882,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="171.6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" ht="165.75" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
         <v>181</v>
       </c>
@@ -7911,7 +7907,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="237.6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" ht="242.25" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
         <v>186</v>
       </c>
@@ -7936,7 +7932,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="132" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" ht="140.25" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
         <v>190</v>
       </c>
@@ -7961,7 +7957,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="66" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A50" s="5" t="s">
         <v>195</v>
       </c>
@@ -7986,7 +7982,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="171.6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" ht="165.75" x14ac:dyDescent="0.2">
       <c r="A51" s="5" t="s">
         <v>199</v>
       </c>
@@ -8011,7 +8007,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="92.4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A52" s="5" t="s">
         <v>204</v>
       </c>
@@ -8036,7 +8032,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="105.6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A53" s="5" t="s">
         <v>208</v>
       </c>
@@ -8061,7 +8057,7 @@
         <v>1786</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="132" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" ht="140.25" x14ac:dyDescent="0.2">
       <c r="A54" s="5" t="s">
         <v>211</v>
       </c>
@@ -8090,7 +8086,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="118.8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A55" s="5" t="s">
         <v>1947</v>
       </c>
@@ -8119,7 +8115,7 @@
         <v>1951</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="92.4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A56" s="5" t="s">
         <v>215</v>
       </c>
@@ -8144,7 +8140,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="132" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A57" s="5" t="s">
         <v>219</v>
       </c>
@@ -8169,7 +8165,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="132" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A58" s="5" t="s">
         <v>223</v>
       </c>
@@ -8194,7 +8190,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="145.19999999999999" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" ht="140.25" x14ac:dyDescent="0.2">
       <c r="A59" s="5" t="s">
         <v>227</v>
       </c>
@@ -8223,7 +8219,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A60" s="5" t="s">
         <v>232</v>
       </c>
@@ -8248,7 +8244,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A61" s="5" t="s">
         <v>235</v>
       </c>
@@ -8273,7 +8269,7 @@
         <v>1787</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="237.6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" ht="242.25" x14ac:dyDescent="0.2">
       <c r="A62" s="5" t="s">
         <v>238</v>
       </c>
@@ -8302,7 +8298,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="145.19999999999999" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" ht="140.25" x14ac:dyDescent="0.2">
       <c r="A63" s="5" t="s">
         <v>242</v>
       </c>
@@ -8327,7 +8323,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A64" s="5" t="s">
         <v>246</v>
       </c>
@@ -8352,7 +8348,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="92.4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A65" s="5" t="s">
         <v>250</v>
       </c>
@@ -8377,7 +8373,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A66" s="5" t="s">
         <v>254</v>
       </c>
@@ -8402,7 +8398,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="105.6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" ht="102" x14ac:dyDescent="0.2">
       <c r="A67" s="5" t="s">
         <v>257</v>
       </c>
@@ -8427,7 +8423,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="118.8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A68" s="5" t="s">
         <v>262</v>
       </c>
@@ -8456,7 +8452,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A69" s="5" t="s">
         <v>267</v>
       </c>
@@ -8481,7 +8477,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="105.6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" ht="102" x14ac:dyDescent="0.2">
       <c r="A70" s="5" t="s">
         <v>272</v>
       </c>
@@ -8506,7 +8502,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="118.8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A71" s="5" t="s">
         <v>277</v>
       </c>
@@ -8531,7 +8527,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="132" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" ht="140.25" x14ac:dyDescent="0.2">
       <c r="A72" s="5" t="s">
         <v>281</v>
       </c>
@@ -8556,7 +8552,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="171.6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" ht="178.5" x14ac:dyDescent="0.2">
       <c r="A73" s="5" t="s">
         <v>285</v>
       </c>
@@ -8585,7 +8581,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="237.6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" ht="242.25" x14ac:dyDescent="0.2">
       <c r="A74" s="5" t="s">
         <v>290</v>
       </c>
@@ -8614,7 +8610,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="66" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A75" s="5" t="s">
         <v>294</v>
       </c>
@@ -8639,7 +8635,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A76" s="5" t="s">
         <v>298</v>
       </c>
@@ -8664,7 +8660,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="118.8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A77" s="5" t="s">
         <v>304</v>
       </c>
@@ -8689,7 +8685,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="132" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A78" s="5" t="s">
         <v>310</v>
       </c>
@@ -8714,7 +8710,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="118.8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A79" s="5" t="s">
         <v>315</v>
       </c>
@@ -8739,7 +8735,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="92.4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A80" s="5" t="s">
         <v>320</v>
       </c>
@@ -8768,7 +8764,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="81" spans="1:9" ht="158.4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" ht="165.75" x14ac:dyDescent="0.2">
       <c r="A81" s="5" t="s">
         <v>326</v>
       </c>
@@ -8797,7 +8793,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="118.8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A82" s="5" t="s">
         <v>330</v>
       </c>
@@ -8826,7 +8822,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="224.4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" ht="216.75" x14ac:dyDescent="0.2">
       <c r="A83" s="5" t="s">
         <v>334</v>
       </c>
@@ -8851,7 +8847,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="118.8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A84" s="5" t="s">
         <v>339</v>
       </c>
@@ -8876,7 +8872,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="105.6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A85" s="5" t="s">
         <v>345</v>
       </c>
@@ -8905,7 +8901,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="92.4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A86" s="5" t="s">
         <v>350</v>
       </c>
@@ -8930,7 +8926,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A87" s="5" t="s">
         <v>356</v>
       </c>
@@ -8955,7 +8951,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A88" s="5" t="s">
         <v>361</v>
       </c>
@@ -8984,7 +8980,7 @@
         <v>1792</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="132" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" ht="140.25" x14ac:dyDescent="0.2">
       <c r="A89" s="5" t="s">
         <v>365</v>
       </c>
@@ -9009,7 +9005,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="90" spans="1:9" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A90" s="5" t="s">
         <v>370</v>
       </c>
@@ -9034,7 +9030,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="145.19999999999999" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" ht="140.25" x14ac:dyDescent="0.2">
       <c r="A91" s="5" t="s">
         <v>375</v>
       </c>
@@ -9059,7 +9055,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="105.6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" ht="102" x14ac:dyDescent="0.2">
       <c r="A92" s="5" t="s">
         <v>378</v>
       </c>
@@ -9088,7 +9084,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="132" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A93" s="5" t="s">
         <v>383</v>
       </c>
@@ -9117,7 +9113,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="211.2" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" ht="216.75" x14ac:dyDescent="0.2">
       <c r="A94" s="5" t="s">
         <v>387</v>
       </c>
@@ -9142,7 +9138,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="92.4" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A95" s="5" t="s">
         <v>391</v>
       </c>
@@ -9171,7 +9167,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="96" spans="1:9" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A96" s="5" t="s">
         <v>395</v>
       </c>
@@ -9200,7 +9196,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="145.19999999999999" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" ht="153" x14ac:dyDescent="0.2">
       <c r="A97" s="5" t="s">
         <v>400</v>
       </c>
@@ -9229,7 +9225,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="118.8" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A98" s="5" t="s">
         <v>404</v>
       </c>
@@ -9254,7 +9250,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="105.6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" ht="102" x14ac:dyDescent="0.2">
       <c r="A99" s="5" t="s">
         <v>409</v>
       </c>
@@ -9279,7 +9275,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="92.4" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A100" s="5" t="s">
         <v>414</v>
       </c>
@@ -9304,7 +9300,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="105.6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" ht="102" x14ac:dyDescent="0.2">
       <c r="A101" s="5" t="s">
         <v>418</v>
       </c>
@@ -9329,7 +9325,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A102" s="5" t="s">
         <v>422</v>
       </c>
@@ -9358,7 +9354,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="132" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A103" s="5" t="s">
         <v>426</v>
       </c>
@@ -9383,7 +9379,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="118.8" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A104" s="5" t="s">
         <v>431</v>
       </c>
@@ -9412,7 +9408,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="105" spans="1:9" ht="105.6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" ht="102" x14ac:dyDescent="0.2">
       <c r="A105" s="5" t="s">
         <v>437</v>
       </c>
@@ -9441,7 +9437,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="132" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A106" s="5" t="s">
         <v>442</v>
       </c>
@@ -9470,7 +9466,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="107" spans="1:9" ht="66" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A107" s="5" t="s">
         <v>447</v>
       </c>
@@ -9495,7 +9491,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="108" spans="1:9" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A108" s="5" t="s">
         <v>451</v>
       </c>
@@ -9520,7 +9516,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="109" spans="1:9" ht="66" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A109" s="5" t="s">
         <v>455</v>
       </c>
@@ -9549,7 +9545,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="110" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A110" s="5" t="s">
         <v>460</v>
       </c>
@@ -9574,7 +9570,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="111" spans="1:9" ht="66" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A111" s="5" t="s">
         <v>464</v>
       </c>
@@ -9603,7 +9599,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="112" spans="1:9" ht="145.19999999999999" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" ht="153" x14ac:dyDescent="0.2">
       <c r="A112" s="5" t="s">
         <v>470</v>
       </c>
@@ -9628,7 +9624,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="113" spans="1:9" ht="118.8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A113" s="5" t="s">
         <v>475</v>
       </c>
@@ -9657,7 +9653,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="114" spans="1:9" ht="158.4" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" ht="153" x14ac:dyDescent="0.2">
       <c r="A114" s="5" t="s">
         <v>480</v>
       </c>
@@ -9686,7 +9682,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="115" spans="1:9" ht="303.60000000000002" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" ht="306" x14ac:dyDescent="0.2">
       <c r="A115" s="5" t="s">
         <v>485</v>
       </c>
@@ -9715,7 +9711,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="116" spans="1:9" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A116" s="5" t="s">
         <v>491</v>
       </c>
@@ -9744,7 +9740,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="117" spans="1:9" ht="66" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A117" s="5" t="s">
         <v>496</v>
       </c>
@@ -9773,7 +9769,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="118" spans="1:9" ht="105.6" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A118" s="5" t="s">
         <v>501</v>
       </c>
@@ -9798,7 +9794,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="119" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A119" s="5" t="s">
         <v>505</v>
       </c>
@@ -9827,7 +9823,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="120" spans="1:9" ht="184.8" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" ht="178.5" x14ac:dyDescent="0.2">
       <c r="A120" s="5" t="s">
         <v>510</v>
       </c>
@@ -9852,7 +9848,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="121" spans="1:9" ht="118.8" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A121" s="5" t="s">
         <v>515</v>
       </c>
@@ -9877,7 +9873,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="122" spans="1:9" ht="171.6" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" ht="165.75" x14ac:dyDescent="0.2">
       <c r="A122" s="5" t="s">
         <v>520</v>
       </c>
@@ -9906,7 +9902,7 @@
         <v>1795</v>
       </c>
     </row>
-    <row r="123" spans="1:9" ht="211.2" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" ht="204" x14ac:dyDescent="0.2">
       <c r="A123" s="5" t="s">
         <v>524</v>
       </c>
@@ -9931,7 +9927,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="124" spans="1:9" ht="118.8" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A124" s="5" t="s">
         <v>529</v>
       </c>
@@ -9956,7 +9952,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="125" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A125" s="5" t="s">
         <v>534</v>
       </c>
@@ -9981,7 +9977,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="126" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A126" s="5" t="s">
         <v>539</v>
       </c>
@@ -10006,7 +10002,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="127" spans="1:9" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A127" s="5" t="s">
         <v>543</v>
       </c>
@@ -10031,7 +10027,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="128" spans="1:9" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A128" s="5" t="s">
         <v>546</v>
       </c>
@@ -10060,7 +10056,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="129" spans="1:9" ht="66" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A129" s="5" t="s">
         <v>551</v>
       </c>
@@ -10085,7 +10081,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="130" spans="1:9" ht="92.4" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A130" s="5" t="s">
         <v>555</v>
       </c>
@@ -10110,7 +10106,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="131" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A131" s="5" t="s">
         <v>561</v>
       </c>
@@ -10135,7 +10131,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="132" spans="1:9" ht="158.4" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" ht="153" x14ac:dyDescent="0.2">
       <c r="A132" s="5" t="s">
         <v>566</v>
       </c>
@@ -10160,7 +10156,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="133" spans="1:9" ht="92.4" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" ht="102" x14ac:dyDescent="0.2">
       <c r="A133" s="5" t="s">
         <v>572</v>
       </c>
@@ -10189,7 +10185,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="134" spans="1:9" ht="105.6" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" ht="102" x14ac:dyDescent="0.2">
       <c r="A134" s="5" t="s">
         <v>577</v>
       </c>
@@ -10218,7 +10214,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="135" spans="1:9" ht="132" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A135" s="5" t="s">
         <v>580</v>
       </c>
@@ -10247,7 +10243,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="136" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A136" s="5" t="s">
         <v>586</v>
       </c>
@@ -10272,7 +10268,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="137" spans="1:9" ht="105.6" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" ht="102" x14ac:dyDescent="0.2">
       <c r="A137" s="5" t="s">
         <v>592</v>
       </c>
@@ -10301,7 +10297,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="138" spans="1:9" ht="118.8" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A138" s="5" t="s">
         <v>597</v>
       </c>
@@ -10330,7 +10326,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="139" spans="1:9" ht="92.4" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A139" s="5" t="s">
         <v>603</v>
       </c>
@@ -10355,7 +10351,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="140" spans="1:9" ht="211.2" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" ht="204" x14ac:dyDescent="0.2">
       <c r="A140" s="5" t="s">
         <v>608</v>
       </c>
@@ -10380,7 +10376,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="141" spans="1:9" ht="132" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" ht="140.25" x14ac:dyDescent="0.2">
       <c r="A141" s="5" t="s">
         <v>613</v>
       </c>
@@ -10405,7 +10401,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="142" spans="1:9" ht="92.4" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A142" s="5" t="s">
         <v>617</v>
       </c>
@@ -10430,7 +10426,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="143" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A143" s="5" t="s">
         <v>622</v>
       </c>
@@ -10455,7 +10451,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="144" spans="1:9" ht="105.6" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A144" s="5" t="s">
         <v>628</v>
       </c>
@@ -10480,7 +10476,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="145" spans="1:9" ht="92.4" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A145" s="5" t="s">
         <v>633</v>
       </c>
@@ -10509,7 +10505,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="146" spans="1:9" ht="105.6" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" ht="102" x14ac:dyDescent="0.2">
       <c r="A146" s="5" t="s">
         <v>636</v>
       </c>
@@ -10534,7 +10530,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="147" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A147" s="5" t="s">
         <v>640</v>
       </c>
@@ -10563,7 +10559,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="148" spans="1:9" ht="105.6" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" ht="102" x14ac:dyDescent="0.2">
       <c r="A148" s="5" t="s">
         <v>645</v>
       </c>
@@ -10588,7 +10584,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="149" spans="1:9" ht="132" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" ht="140.25" x14ac:dyDescent="0.2">
       <c r="A149" s="5" t="s">
         <v>649</v>
       </c>
@@ -10613,7 +10609,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="150" spans="1:9" ht="132" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" ht="140.25" x14ac:dyDescent="0.2">
       <c r="A150" s="5" t="s">
         <v>653</v>
       </c>
@@ -10638,7 +10634,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="151" spans="1:9" ht="118.8" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A151" s="5" t="s">
         <v>657</v>
       </c>
@@ -10663,7 +10659,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="152" spans="1:9" ht="105.6" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" ht="102" x14ac:dyDescent="0.2">
       <c r="A152" s="5" t="s">
         <v>662</v>
       </c>
@@ -10692,7 +10688,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="153" spans="1:9" ht="237.6" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" ht="229.5" x14ac:dyDescent="0.2">
       <c r="A153" s="5" t="s">
         <v>665</v>
       </c>
@@ -10717,7 +10713,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="154" spans="1:9" ht="145.19999999999999" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" ht="140.25" x14ac:dyDescent="0.2">
       <c r="A154" s="5" t="s">
         <v>669</v>
       </c>
@@ -10746,7 +10742,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="155" spans="1:9" ht="158.4" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" ht="153" x14ac:dyDescent="0.2">
       <c r="A155" s="5" t="s">
         <v>675</v>
       </c>
@@ -10775,7 +10771,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="156" spans="1:9" ht="92.4" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" ht="102" x14ac:dyDescent="0.2">
       <c r="A156" s="5" t="s">
         <v>680</v>
       </c>
@@ -10804,7 +10800,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="157" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A157" s="5" t="s">
         <v>685</v>
       </c>
@@ -10833,7 +10829,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="158" spans="1:9" ht="105.6" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" ht="102" x14ac:dyDescent="0.2">
       <c r="A158" s="5" t="s">
         <v>690</v>
       </c>
@@ -10862,7 +10858,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="159" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A159" s="5" t="s">
         <v>695</v>
       </c>
@@ -10891,7 +10887,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="160" spans="1:9" ht="105.6" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" ht="102" x14ac:dyDescent="0.2">
       <c r="A160" s="5" t="s">
         <v>700</v>
       </c>
@@ -10920,7 +10916,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="161" spans="1:9" ht="198" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" ht="191.25" x14ac:dyDescent="0.2">
       <c r="A161" s="5" t="s">
         <v>704</v>
       </c>
@@ -10949,7 +10945,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="162" spans="1:9" ht="198" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" ht="191.25" x14ac:dyDescent="0.2">
       <c r="A162" s="5" t="s">
         <v>709</v>
       </c>
@@ -10974,7 +10970,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="163" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A163" s="5" t="s">
         <v>713</v>
       </c>
@@ -11003,7 +10999,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="164" spans="1:9" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A164" s="5" t="s">
         <v>718</v>
       </c>
@@ -11028,7 +11024,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="165" spans="1:9" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A165" s="5" t="s">
         <v>722</v>
       </c>
@@ -11053,7 +11049,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="166" spans="1:9" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A166" s="5" t="s">
         <v>727</v>
       </c>
@@ -11078,7 +11074,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="167" spans="1:9" ht="105.6" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" ht="102" x14ac:dyDescent="0.2">
       <c r="A167" s="5" t="s">
         <v>731</v>
       </c>
@@ -11103,7 +11099,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="168" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A168" s="5" t="s">
         <v>735</v>
       </c>
@@ -11132,7 +11128,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="169" spans="1:9" ht="66" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A169" s="5" t="s">
         <v>743</v>
       </c>
@@ -11157,7 +11153,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="170" spans="1:9" ht="145.19999999999999" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" ht="140.25" x14ac:dyDescent="0.2">
       <c r="A170" s="5" t="s">
         <v>747</v>
       </c>
@@ -11186,7 +11182,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="171" spans="1:9" ht="118.8" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A171" s="5" t="s">
         <v>751</v>
       </c>
@@ -11211,7 +11207,7 @@
         <v>1790</v>
       </c>
     </row>
-    <row r="172" spans="1:9" ht="132" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A172" s="5" t="s">
         <v>754</v>
       </c>
@@ -11240,7 +11236,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="173" spans="1:9" ht="145.19999999999999" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" ht="140.25" x14ac:dyDescent="0.2">
       <c r="A173" s="5" t="s">
         <v>758</v>
       </c>
@@ -11265,7 +11261,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="174" spans="1:9" ht="92.4" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" ht="102" x14ac:dyDescent="0.2">
       <c r="A174" s="5" t="s">
         <v>762</v>
       </c>
@@ -11294,7 +11290,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="175" spans="1:9" ht="145.19999999999999" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" ht="140.25" x14ac:dyDescent="0.2">
       <c r="A175" s="5" t="s">
         <v>768</v>
       </c>
@@ -11319,7 +11315,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="176" spans="1:9" ht="224.4" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" ht="229.5" x14ac:dyDescent="0.2">
       <c r="A176" s="5" t="s">
         <v>772</v>
       </c>
@@ -11344,7 +11340,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="177" spans="1:9" ht="92.4" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9" ht="102" x14ac:dyDescent="0.2">
       <c r="A177" s="5" t="s">
         <v>777</v>
       </c>
@@ -11369,7 +11365,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="178" spans="1:9" ht="92.4" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:9" ht="102" x14ac:dyDescent="0.2">
       <c r="A178" s="5" t="s">
         <v>783</v>
       </c>
@@ -11394,7 +11390,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="179" spans="1:9" ht="105.6" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9" ht="102" x14ac:dyDescent="0.2">
       <c r="A179" s="5" t="s">
         <v>788</v>
       </c>
@@ -11423,7 +11419,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="180" spans="1:9" ht="92.4" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:9" ht="102" x14ac:dyDescent="0.2">
       <c r="A180" s="5" t="s">
         <v>793</v>
       </c>
@@ -11448,7 +11444,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="181" spans="1:9" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A181" s="5" t="s">
         <v>799</v>
       </c>
@@ -11477,7 +11473,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="182" spans="1:9" ht="171.6" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9" ht="165.75" x14ac:dyDescent="0.2">
       <c r="A182" s="5" t="s">
         <v>804</v>
       </c>
@@ -11506,7 +11502,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="183" spans="1:9" ht="198" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9" ht="204" x14ac:dyDescent="0.2">
       <c r="A183" s="5" t="s">
         <v>810</v>
       </c>
@@ -11531,7 +11527,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="184" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A184" s="5" t="s">
         <v>816</v>
       </c>
@@ -11556,7 +11552,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="185" spans="1:9" ht="237.6" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9" ht="242.25" x14ac:dyDescent="0.2">
       <c r="A185" s="5" t="s">
         <v>820</v>
       </c>
@@ -11585,7 +11581,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="186" spans="1:9" ht="171.6" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9" ht="178.5" x14ac:dyDescent="0.2">
       <c r="A186" s="5" t="s">
         <v>824</v>
       </c>
@@ -11610,7 +11606,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="187" spans="1:9" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A187" s="5" t="s">
         <v>830</v>
       </c>
@@ -11639,7 +11635,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="188" spans="1:9" ht="66" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A188" s="5" t="s">
         <v>836</v>
       </c>
@@ -11664,7 +11660,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="189" spans="1:9" ht="184.8" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9" ht="178.5" x14ac:dyDescent="0.2">
       <c r="A189" s="5" t="s">
         <v>841</v>
       </c>
@@ -11689,7 +11685,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="190" spans="1:9" ht="118.8" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A190" s="5" t="s">
         <v>845</v>
       </c>
@@ -11718,7 +11714,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="191" spans="1:9" ht="132" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A191" s="5" t="s">
         <v>849</v>
       </c>
@@ -11743,7 +11739,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="192" spans="1:9" ht="66" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A192" s="5" t="s">
         <v>853</v>
       </c>
@@ -11772,7 +11768,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="193" spans="1:9" ht="145.19999999999999" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" ht="140.25" x14ac:dyDescent="0.2">
       <c r="A193" s="5" t="s">
         <v>857</v>
       </c>
@@ -11801,7 +11797,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="194" spans="1:9" ht="158.4" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" ht="165.75" x14ac:dyDescent="0.2">
       <c r="A194" s="5" t="s">
         <v>861</v>
       </c>
@@ -11826,7 +11822,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="195" spans="1:9" ht="158.4" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" ht="153" x14ac:dyDescent="0.2">
       <c r="A195" s="5" t="s">
         <v>865</v>
       </c>
@@ -11851,7 +11847,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="196" spans="1:9" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A196" s="5" t="s">
         <v>869</v>
       </c>
@@ -11876,7 +11872,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="197" spans="1:9" ht="92.4" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A197" s="5" t="s">
         <v>874</v>
       </c>
@@ -11901,7 +11897,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="198" spans="1:9" ht="105.6" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" ht="102" x14ac:dyDescent="0.2">
       <c r="A198" s="5" t="s">
         <v>878</v>
       </c>
@@ -11930,7 +11926,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="199" spans="1:9" ht="132" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A199" s="5" t="s">
         <v>882</v>
       </c>
@@ -11955,7 +11951,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="200" spans="1:9" ht="118.8" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A200" s="5" t="s">
         <v>886</v>
       </c>
@@ -11980,7 +11976,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="201" spans="1:9" ht="105.6" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" ht="102" x14ac:dyDescent="0.2">
       <c r="A201" s="5" t="s">
         <v>890</v>
       </c>
@@ -12005,7 +12001,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="202" spans="1:9" ht="105.6" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" ht="102" x14ac:dyDescent="0.2">
       <c r="A202" s="5" t="s">
         <v>896</v>
       </c>
@@ -12034,7 +12030,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="203" spans="1:9" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A203" s="5" t="s">
         <v>900</v>
       </c>
@@ -12059,7 +12055,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="204" spans="1:9" ht="105.6" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" ht="102" x14ac:dyDescent="0.2">
       <c r="A204" s="5" t="s">
         <v>905</v>
       </c>
@@ -12084,7 +12080,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="205" spans="1:9" ht="224.4" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" ht="229.5" x14ac:dyDescent="0.2">
       <c r="A205" s="5" t="s">
         <v>910</v>
       </c>
@@ -12109,7 +12105,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="206" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A206" s="5" t="s">
         <v>914</v>
       </c>
@@ -12134,7 +12130,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="207" spans="1:9" ht="224.4" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" ht="216.75" x14ac:dyDescent="0.2">
       <c r="A207" s="5" t="s">
         <v>919</v>
       </c>
@@ -12159,7 +12155,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="208" spans="1:9" ht="145.19999999999999" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9" ht="140.25" x14ac:dyDescent="0.2">
       <c r="A208" s="5" t="s">
         <v>922</v>
       </c>
@@ -12184,7 +12180,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="209" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A209" s="5" t="s">
         <v>926</v>
       </c>
@@ -12213,7 +12209,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="210" spans="1:9" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A210" s="5" t="s">
         <v>930</v>
       </c>
@@ -12242,7 +12238,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="211" spans="1:9" ht="171.6" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" ht="165.75" x14ac:dyDescent="0.2">
       <c r="A211" s="5" t="s">
         <v>934</v>
       </c>
@@ -12267,7 +12263,7 @@
         <v>939</v>
       </c>
     </row>
-    <row r="212" spans="1:9" ht="118.8" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A212" s="5" t="s">
         <v>940</v>
       </c>
@@ -12292,7 +12288,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="213" spans="1:9" ht="184.8" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" ht="178.5" x14ac:dyDescent="0.2">
       <c r="A213" s="5" t="s">
         <v>944</v>
       </c>
@@ -12321,7 +12317,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="214" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A214" s="5" t="s">
         <v>949</v>
       </c>
@@ -12350,7 +12346,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="215" spans="1:9" ht="66" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A215" s="5" t="s">
         <v>954</v>
       </c>
@@ -12375,7 +12371,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="216" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A216" s="5" t="s">
         <v>959</v>
       </c>
@@ -12400,7 +12396,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="217" spans="1:9" ht="105.6" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" ht="102" x14ac:dyDescent="0.2">
       <c r="A217" s="5" t="s">
         <v>964</v>
       </c>
@@ -12425,7 +12421,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="218" spans="1:9" ht="118.8" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A218" s="5" t="s">
         <v>969</v>
       </c>
@@ -12450,7 +12446,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="219" spans="1:9" ht="105.6" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" ht="102" x14ac:dyDescent="0.2">
       <c r="A219" s="5" t="s">
         <v>975</v>
       </c>
@@ -12475,7 +12471,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="220" spans="1:9" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A220" s="5" t="s">
         <v>980</v>
       </c>
@@ -12500,7 +12496,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="221" spans="1:9" ht="145.19999999999999" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9" ht="153" x14ac:dyDescent="0.2">
       <c r="A221" s="5" t="s">
         <v>986</v>
       </c>
@@ -12525,7 +12521,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="222" spans="1:9" ht="105.6" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" ht="102" x14ac:dyDescent="0.2">
       <c r="A222" s="5" t="s">
         <v>991</v>
       </c>
@@ -12550,7 +12546,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="223" spans="1:9" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A223" s="5" t="s">
         <v>996</v>
       </c>
@@ -12575,7 +12571,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="224" spans="1:9" ht="145.19999999999999" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" ht="140.25" x14ac:dyDescent="0.2">
       <c r="A224" s="5" t="s">
         <v>1001</v>
       </c>
@@ -12600,7 +12596,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="225" spans="1:9" ht="92.4" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A225" s="5" t="s">
         <v>1005</v>
       </c>
@@ -12629,7 +12625,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="226" spans="1:9" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A226" s="5" t="s">
         <v>1009</v>
       </c>
@@ -12658,7 +12654,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="227" spans="1:9" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A227" s="5" t="s">
         <v>1014</v>
       </c>
@@ -12683,7 +12679,7 @@
         <v>1018</v>
       </c>
     </row>
-    <row r="228" spans="1:9" ht="66" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A228" s="5" t="s">
         <v>1019</v>
       </c>
@@ -12708,7 +12704,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="229" spans="1:9" ht="158.4" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:9" ht="153" x14ac:dyDescent="0.2">
       <c r="A229" s="5" t="s">
         <v>1023</v>
       </c>
@@ -12733,7 +12729,7 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="230" spans="1:9" ht="132" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:9" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A230" s="5" t="s">
         <v>1028</v>
       </c>
@@ -12758,7 +12754,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="231" spans="1:9" ht="118.8" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A231" s="5" t="s">
         <v>1033</v>
       </c>
@@ -12787,7 +12783,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="232" spans="1:9" ht="105.6" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9" ht="102" x14ac:dyDescent="0.2">
       <c r="A232" s="5" t="s">
         <v>1038</v>
       </c>
@@ -12816,7 +12812,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="233" spans="1:9" ht="171.6" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9" ht="165.75" x14ac:dyDescent="0.2">
       <c r="A233" s="5" t="s">
         <v>1042</v>
       </c>
@@ -12841,7 +12837,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="234" spans="1:9" ht="66" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A234" s="5" t="s">
         <v>1046</v>
       </c>
@@ -12870,7 +12866,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="235" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:9" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A235" s="5" t="s">
         <v>1052</v>
       </c>
@@ -12895,7 +12891,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="236" spans="1:9" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:9" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A236" s="5" t="s">
         <v>1057</v>
       </c>
@@ -12924,7 +12920,7 @@
         <v>1060</v>
       </c>
     </row>
-    <row r="237" spans="1:9" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:9" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A237" s="5" t="s">
         <v>1061</v>
       </c>
@@ -12949,7 +12945,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="238" spans="1:9" ht="105.6" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:9" ht="102" x14ac:dyDescent="0.2">
       <c r="A238" s="5" t="s">
         <v>1066</v>
       </c>
@@ -12974,7 +12970,7 @@
         <v>1071</v>
       </c>
     </row>
-    <row r="239" spans="1:9" ht="118.8" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:9" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A239" s="5" t="s">
         <v>1072</v>
       </c>
@@ -12999,7 +12995,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="240" spans="1:9" ht="66" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:9" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A240" s="5" t="s">
         <v>1076</v>
       </c>
@@ -13024,7 +13020,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="241" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:9" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A241" s="5" t="s">
         <v>1081</v>
       </c>
@@ -13049,7 +13045,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="242" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:9" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A242" s="5" t="s">
         <v>1087</v>
       </c>
@@ -13074,7 +13070,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="243" spans="1:9" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:9" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A243" s="5" t="s">
         <v>1092</v>
       </c>
@@ -13103,7 +13099,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="244" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:9" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A244" s="5" t="s">
         <v>1097</v>
       </c>
@@ -13132,7 +13128,7 @@
         <v>1102</v>
       </c>
     </row>
-    <row r="245" spans="1:9" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A245" s="5" t="s">
         <v>1103</v>
       </c>
@@ -13157,7 +13153,7 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="246" spans="1:9" ht="92.4" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:9" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A246" s="5" t="s">
         <v>1108</v>
       </c>
@@ -13182,7 +13178,7 @@
         <v>1112</v>
       </c>
     </row>
-    <row r="247" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:9" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A247" s="5" t="s">
         <v>1113</v>
       </c>
@@ -13211,7 +13207,7 @@
         <v>1117</v>
       </c>
     </row>
-    <row r="248" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:9" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A248" s="5" t="s">
         <v>1118</v>
       </c>
@@ -13236,7 +13232,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="249" spans="1:9" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A249" s="5" t="s">
         <v>1122</v>
       </c>
@@ -13261,7 +13257,7 @@
         <v>1126</v>
       </c>
     </row>
-    <row r="250" spans="1:9" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A250" s="5" t="s">
         <v>1127</v>
       </c>
@@ -13286,7 +13282,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="251" spans="1:9" ht="66" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:9" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A251" s="5" t="s">
         <v>1132</v>
       </c>
@@ -13315,7 +13311,7 @@
         <v>1137</v>
       </c>
     </row>
-    <row r="252" spans="1:9" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:9" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A252" s="5" t="s">
         <v>1138</v>
       </c>
@@ -13344,7 +13340,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="253" spans="1:9" ht="158.4" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:9" ht="165.75" x14ac:dyDescent="0.2">
       <c r="A253" s="5" t="s">
         <v>1143</v>
       </c>
@@ -13369,7 +13365,7 @@
         <v>1147</v>
       </c>
     </row>
-    <row r="254" spans="1:9" ht="132" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:9" ht="140.25" x14ac:dyDescent="0.2">
       <c r="A254" s="5" t="s">
         <v>1148</v>
       </c>
@@ -13394,7 +13390,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="255" spans="1:9" ht="158.4" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:9" ht="153" x14ac:dyDescent="0.2">
       <c r="A255" s="5" t="s">
         <v>1152</v>
       </c>
@@ -13419,7 +13415,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="256" spans="1:9" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:9" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A256" s="5" t="s">
         <v>1157</v>
       </c>
@@ -13448,7 +13444,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="257" spans="1:9" ht="132" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:9" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A257" s="5" t="s">
         <v>1161</v>
       </c>
@@ -13473,7 +13469,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="258" spans="1:9" ht="132" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:9" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A258" s="5" t="s">
         <v>1166</v>
       </c>
@@ -13498,7 +13494,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="259" spans="1:9" ht="158.4" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:9" ht="153" x14ac:dyDescent="0.2">
       <c r="A259" s="5" t="s">
         <v>1170</v>
       </c>
@@ -13523,7 +13519,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="260" spans="1:9" ht="105.6" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:9" ht="102" x14ac:dyDescent="0.2">
       <c r="A260" s="5" t="s">
         <v>1175</v>
       </c>
@@ -13548,7 +13544,7 @@
         <v>1179</v>
       </c>
     </row>
-    <row r="261" spans="1:9" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A261" s="5" t="s">
         <v>1180</v>
       </c>
@@ -13573,7 +13569,7 @@
         <v>1184</v>
       </c>
     </row>
-    <row r="262" spans="1:9" ht="66" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:9" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A262" s="5" t="s">
         <v>1185</v>
       </c>
@@ -13598,7 +13594,7 @@
         <v>1188</v>
       </c>
     </row>
-    <row r="263" spans="1:9" ht="118.8" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:9" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A263" s="5" t="s">
         <v>1189</v>
       </c>
@@ -13623,7 +13619,7 @@
         <v>1192</v>
       </c>
     </row>
-    <row r="264" spans="1:9" ht="132" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:9" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A264" s="5" t="s">
         <v>1193</v>
       </c>
@@ -13648,7 +13644,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="265" spans="1:9" ht="158.4" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:9" ht="165.75" x14ac:dyDescent="0.2">
       <c r="A265" s="5" t="s">
         <v>1197</v>
       </c>
@@ -13673,7 +13669,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="266" spans="1:9" ht="105.6" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:9" ht="102" x14ac:dyDescent="0.2">
       <c r="A266" s="5" t="s">
         <v>1201</v>
       </c>
@@ -13702,7 +13698,7 @@
         <v>1205</v>
       </c>
     </row>
-    <row r="267" spans="1:9" ht="145.19999999999999" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:9" ht="153" x14ac:dyDescent="0.2">
       <c r="A267" s="5" t="s">
         <v>1206</v>
       </c>
@@ -13727,7 +13723,7 @@
         <v>1211</v>
       </c>
     </row>
-    <row r="268" spans="1:9" ht="184.8" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:9" ht="178.5" x14ac:dyDescent="0.2">
       <c r="A268" s="5" t="s">
         <v>1212</v>
       </c>
@@ -13756,7 +13752,7 @@
         <v>1215</v>
       </c>
     </row>
-    <row r="269" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:9" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A269" s="5" t="s">
         <v>1216</v>
       </c>
@@ -13781,7 +13777,7 @@
         <v>1219</v>
       </c>
     </row>
-    <row r="270" spans="1:9" ht="118.8" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:9" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A270" s="5" t="s">
         <v>1220</v>
       </c>
@@ -13810,7 +13806,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="271" spans="1:9" ht="224.4" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:9" ht="229.5" x14ac:dyDescent="0.2">
       <c r="A271" s="5" t="s">
         <v>1225</v>
       </c>
@@ -13839,7 +13835,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="272" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:9" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A272" s="5" t="s">
         <v>1230</v>
       </c>
@@ -13868,7 +13864,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="273" spans="1:9" ht="105.6" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:9" ht="102" x14ac:dyDescent="0.2">
       <c r="A273" s="5" t="s">
         <v>1234</v>
       </c>
@@ -13897,7 +13893,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="274" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:9" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A274" s="5" t="s">
         <v>1238</v>
       </c>
@@ -13922,7 +13918,7 @@
         <v>1241</v>
       </c>
     </row>
-    <row r="275" spans="1:9" ht="132" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:9" ht="140.25" x14ac:dyDescent="0.2">
       <c r="A275" s="5" t="s">
         <v>1242</v>
       </c>
@@ -13947,7 +13943,7 @@
         <v>1246</v>
       </c>
     </row>
-    <row r="276" spans="1:9" ht="92.4" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:9" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A276" s="5" t="s">
         <v>1247</v>
       </c>
@@ -13976,7 +13972,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="277" spans="1:9" ht="105.6" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:9" ht="102" x14ac:dyDescent="0.2">
       <c r="A277" s="5" t="s">
         <v>1253</v>
       </c>
@@ -14005,7 +14001,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="278" spans="1:9" ht="118.8" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:9" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A278" s="5" t="s">
         <v>1257</v>
       </c>
@@ -14030,7 +14026,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="279" spans="1:9" ht="145.19999999999999" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:9" ht="140.25" x14ac:dyDescent="0.2">
       <c r="A279" s="5" t="s">
         <v>1261</v>
       </c>
@@ -14055,7 +14051,7 @@
         <v>1264</v>
       </c>
     </row>
-    <row r="280" spans="1:9" ht="145.19999999999999" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:9" ht="140.25" x14ac:dyDescent="0.2">
       <c r="A280" s="5" t="s">
         <v>1265</v>
       </c>
@@ -14084,7 +14080,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="281" spans="1:9" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:9" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A281" s="5" t="s">
         <v>1269</v>
       </c>
@@ -14109,7 +14105,7 @@
         <v>1272</v>
       </c>
     </row>
-    <row r="282" spans="1:9" ht="118.8" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:9" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A282" s="5" t="s">
         <v>1273</v>
       </c>
@@ -14134,7 +14130,7 @@
         <v>1276</v>
       </c>
     </row>
-    <row r="283" spans="1:9" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:9" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A283" s="5" t="s">
         <v>1277</v>
       </c>
@@ -14159,7 +14155,7 @@
         <v>1280</v>
       </c>
     </row>
-    <row r="284" spans="1:9" ht="171.6" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:9" ht="165.75" x14ac:dyDescent="0.2">
       <c r="A284" s="5" t="s">
         <v>1281</v>
       </c>
@@ -14184,7 +14180,7 @@
         <v>1284</v>
       </c>
     </row>
-    <row r="285" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:9" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A285" s="5" t="s">
         <v>1285</v>
       </c>
@@ -14213,7 +14209,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="286" spans="1:9" ht="171.6" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:9" ht="178.5" x14ac:dyDescent="0.2">
       <c r="A286" s="5" t="s">
         <v>1289</v>
       </c>
@@ -14242,7 +14238,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="287" spans="1:9" ht="145.19999999999999" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:9" ht="140.25" x14ac:dyDescent="0.2">
       <c r="A287" s="5" t="s">
         <v>1293</v>
       </c>
@@ -14271,7 +14267,7 @@
         <v>1296</v>
       </c>
     </row>
-    <row r="288" spans="1:9" ht="250.8" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:9" ht="242.25" x14ac:dyDescent="0.2">
       <c r="A288" s="5" t="s">
         <v>1297</v>
       </c>
@@ -14296,7 +14292,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="289" spans="1:9" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:9" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A289" s="5" t="s">
         <v>1301</v>
       </c>
@@ -14321,7 +14317,7 @@
         <v>1304</v>
       </c>
     </row>
-    <row r="290" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:9" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A290" s="5" t="s">
         <v>1305</v>
       </c>
@@ -14346,7 +14342,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="291" spans="1:9" ht="158.4" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:9" ht="165.75" x14ac:dyDescent="0.2">
       <c r="A291" s="5" t="s">
         <v>1309</v>
       </c>
@@ -14371,7 +14367,7 @@
         <v>1312</v>
       </c>
     </row>
-    <row r="292" spans="1:9" ht="184.8" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:9" ht="178.5" x14ac:dyDescent="0.2">
       <c r="A292" s="5" t="s">
         <v>1313</v>
       </c>
@@ -14396,7 +14392,7 @@
         <v>1316</v>
       </c>
     </row>
-    <row r="293" spans="1:9" ht="158.4" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:9" ht="153" x14ac:dyDescent="0.2">
       <c r="A293" s="5" t="s">
         <v>1317</v>
       </c>
@@ -14421,7 +14417,7 @@
         <v>1320</v>
       </c>
     </row>
-    <row r="294" spans="1:9" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A294" s="5" t="s">
         <v>1321</v>
       </c>
@@ -14446,7 +14442,7 @@
         <v>1323</v>
       </c>
     </row>
-    <row r="295" spans="1:9" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:9" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A295" s="5" t="s">
         <v>1324</v>
       </c>
@@ -14475,7 +14471,7 @@
         <v>1327</v>
       </c>
     </row>
-    <row r="296" spans="1:9" ht="66" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:9" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A296" s="5" t="s">
         <v>1328</v>
       </c>
@@ -14500,7 +14496,7 @@
         <v>1331</v>
       </c>
     </row>
-    <row r="297" spans="1:9" ht="66" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:9" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A297" s="5" t="s">
         <v>1332</v>
       </c>
@@ -14525,7 +14521,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="298" spans="1:9" ht="132" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:9" ht="140.25" x14ac:dyDescent="0.2">
       <c r="A298" s="5" t="s">
         <v>1336</v>
       </c>
@@ -14554,7 +14550,7 @@
         <v>1339</v>
       </c>
     </row>
-    <row r="299" spans="1:9" ht="105.6" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:9" ht="102" x14ac:dyDescent="0.2">
       <c r="A299" s="5" t="s">
         <v>1340</v>
       </c>
@@ -14583,7 +14579,7 @@
         <v>1343</v>
       </c>
     </row>
-    <row r="300" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A300" s="5" t="s">
         <v>1960</v>
       </c>
@@ -14612,7 +14608,7 @@
         <v>1959</v>
       </c>
     </row>
-    <row r="301" spans="1:9" ht="198" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:9" ht="191.25" x14ac:dyDescent="0.2">
       <c r="A301" s="5" t="s">
         <v>1344</v>
       </c>
@@ -14641,7 +14637,7 @@
         <v>1347</v>
       </c>
     </row>
-    <row r="302" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:9" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A302" s="5" t="s">
         <v>1348</v>
       </c>
@@ -14666,7 +14662,7 @@
         <v>1351</v>
       </c>
     </row>
-    <row r="303" spans="1:9" ht="158.4" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:9" ht="153" x14ac:dyDescent="0.2">
       <c r="A303" s="5" t="s">
         <v>1352</v>
       </c>
@@ -14695,7 +14691,7 @@
         <v>1355</v>
       </c>
     </row>
-    <row r="304" spans="1:9" ht="132" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:9" ht="140.25" x14ac:dyDescent="0.2">
       <c r="A304" s="5" t="s">
         <v>1952</v>
       </c>
@@ -14724,7 +14720,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="305" spans="1:9" ht="105.6" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:9" ht="102" x14ac:dyDescent="0.2">
       <c r="A305" s="5" t="s">
         <v>1357</v>
       </c>
@@ -14753,7 +14749,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="306" spans="1:9" ht="66" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:9" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A306" s="5" t="s">
         <v>1361</v>
       </c>
@@ -14782,7 +14778,7 @@
         <v>1364</v>
       </c>
     </row>
-    <row r="307" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:9" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A307" s="5" t="s">
         <v>1365</v>
       </c>
@@ -14807,7 +14803,7 @@
         <v>1368</v>
       </c>
     </row>
-    <row r="308" spans="1:9" ht="132" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:9" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A308" s="5" t="s">
         <v>1369</v>
       </c>
@@ -14836,7 +14832,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="309" spans="1:9" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A309" s="5" t="s">
         <v>1373</v>
       </c>
@@ -14861,7 +14857,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="310" spans="1:9" ht="132" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:9" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A310" s="5" t="s">
         <v>1377</v>
       </c>
@@ -14886,7 +14882,7 @@
         <v>1380</v>
       </c>
     </row>
-    <row r="311" spans="1:9" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:9" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A311" s="5" t="s">
         <v>1381</v>
       </c>
@@ -14911,7 +14907,7 @@
         <v>1384</v>
       </c>
     </row>
-    <row r="312" spans="1:9" ht="237.6" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:9" ht="229.5" x14ac:dyDescent="0.2">
       <c r="A312" s="5" t="s">
         <v>1385</v>
       </c>
@@ -14936,7 +14932,7 @@
         <v>1388</v>
       </c>
     </row>
-    <row r="313" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:9" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A313" s="5" t="s">
         <v>1389</v>
       </c>
@@ -14961,7 +14957,7 @@
         <v>1392</v>
       </c>
     </row>
-    <row r="314" spans="1:9" ht="105.6" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:9" ht="102" x14ac:dyDescent="0.2">
       <c r="A314" s="5" t="s">
         <v>1393</v>
       </c>
@@ -14986,7 +14982,7 @@
         <v>1396</v>
       </c>
     </row>
-    <row r="315" spans="1:9" ht="145.19999999999999" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:9" ht="140.25" x14ac:dyDescent="0.2">
       <c r="A315" s="5" t="s">
         <v>1397</v>
       </c>
@@ -15011,7 +15007,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="316" spans="1:9" ht="118.8" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:9" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A316" s="5" t="s">
         <v>1401</v>
       </c>
@@ -15036,7 +15032,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="317" spans="1:9" ht="66" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:9" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A317" s="5" t="s">
         <v>1405</v>
       </c>
@@ -15061,7 +15057,7 @@
         <v>1408</v>
       </c>
     </row>
-    <row r="318" spans="1:9" ht="198" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:9" ht="204" x14ac:dyDescent="0.2">
       <c r="A318" s="5" t="s">
         <v>1409</v>
       </c>
@@ -15086,7 +15082,7 @@
         <v>1412</v>
       </c>
     </row>
-    <row r="319" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:9" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A319" s="5" t="s">
         <v>1413</v>
       </c>
@@ -15111,7 +15107,7 @@
         <v>1788</v>
       </c>
     </row>
-    <row r="320" spans="1:9" ht="118.8" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:9" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A320" s="5" t="s">
         <v>1416</v>
       </c>
@@ -15140,7 +15136,7 @@
         <v>1419</v>
       </c>
     </row>
-    <row r="321" spans="1:9" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:9" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A321" s="5" t="s">
         <v>1420</v>
       </c>
@@ -15165,7 +15161,7 @@
         <v>1423</v>
       </c>
     </row>
-    <row r="322" spans="1:9" ht="250.8" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:9" ht="242.25" x14ac:dyDescent="0.2">
       <c r="A322" s="5" t="s">
         <v>1424</v>
       </c>
@@ -15194,7 +15190,7 @@
         <v>1427</v>
       </c>
     </row>
-    <row r="323" spans="1:9" ht="158.4" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:9" ht="153" x14ac:dyDescent="0.2">
       <c r="A323" s="5" t="s">
         <v>1428</v>
       </c>
@@ -15219,7 +15215,7 @@
         <v>1431</v>
       </c>
     </row>
-    <row r="324" spans="1:9" ht="198" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:9" ht="191.25" x14ac:dyDescent="0.2">
       <c r="A324" s="5" t="s">
         <v>1432</v>
       </c>
@@ -15248,7 +15244,7 @@
         <v>1435</v>
       </c>
     </row>
-    <row r="325" spans="1:9" ht="132" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:9" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A325" s="5" t="s">
         <v>1436</v>
       </c>
@@ -15277,7 +15273,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="326" spans="1:9" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:9" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A326" s="5" t="s">
         <v>1440</v>
       </c>
@@ -15306,7 +15302,7 @@
         <v>1443</v>
       </c>
     </row>
-    <row r="327" spans="1:9" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A327" s="5" t="s">
         <v>1444</v>
       </c>
@@ -15335,7 +15331,7 @@
         <v>1789</v>
       </c>
     </row>
-    <row r="328" spans="1:9" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:9" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A328" s="5" t="s">
         <v>1447</v>
       </c>
@@ -15360,7 +15356,7 @@
         <v>1450</v>
       </c>
     </row>
-    <row r="329" spans="1:9" ht="92.4" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:9" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A329" s="5" t="s">
         <v>1451</v>
       </c>
@@ -15385,7 +15381,7 @@
         <v>1454</v>
       </c>
     </row>
-    <row r="330" spans="1:9" ht="118.8" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:9" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A330" s="5" t="s">
         <v>1455</v>
       </c>
@@ -15410,7 +15406,7 @@
         <v>1458</v>
       </c>
     </row>
-    <row r="331" spans="1:9" ht="92.4" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:9" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A331" s="5" t="s">
         <v>1459</v>
       </c>
@@ -15439,7 +15435,7 @@
         <v>1462</v>
       </c>
     </row>
-    <row r="332" spans="1:9" ht="211.2" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:9" ht="216.75" x14ac:dyDescent="0.2">
       <c r="A332" s="5" t="s">
         <v>1463</v>
       </c>
@@ -15468,7 +15464,7 @@
         <v>1466</v>
       </c>
     </row>
-    <row r="333" spans="1:9" ht="132" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:9" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A333" s="5" t="s">
         <v>1467</v>
       </c>
@@ -15497,7 +15493,7 @@
         <v>1470</v>
       </c>
     </row>
-    <row r="334" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:9" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A334" s="5" t="s">
         <v>1471</v>
       </c>
@@ -15522,7 +15518,7 @@
         <v>1474</v>
       </c>
     </row>
-    <row r="335" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:9" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A335" s="5" t="s">
         <v>1475</v>
       </c>
@@ -15551,7 +15547,7 @@
         <v>1478</v>
       </c>
     </row>
-    <row r="336" spans="1:9" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:9" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A336" s="5" t="s">
         <v>1479</v>
       </c>
@@ -15576,7 +15572,7 @@
         <v>1482</v>
       </c>
     </row>
-    <row r="337" spans="1:9" ht="158.4" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:9" ht="153" x14ac:dyDescent="0.2">
       <c r="A337" s="5" t="s">
         <v>1483</v>
       </c>
@@ -15601,7 +15597,7 @@
         <v>1486</v>
       </c>
     </row>
-    <row r="338" spans="1:9" ht="171.6" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:9" ht="165.75" x14ac:dyDescent="0.2">
       <c r="A338" s="5" t="s">
         <v>1487</v>
       </c>
@@ -15626,7 +15622,7 @@
         <v>1490</v>
       </c>
     </row>
-    <row r="339" spans="1:9" ht="118.8" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:9" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A339" s="5" t="s">
         <v>1491</v>
       </c>
@@ -15655,7 +15651,7 @@
         <v>1494</v>
       </c>
     </row>
-    <row r="340" spans="1:9" ht="92.4" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:9" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A340" s="5" t="s">
         <v>1495</v>
       </c>
@@ -15684,7 +15680,7 @@
         <v>1498</v>
       </c>
     </row>
-    <row r="341" spans="1:9" ht="132" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:9" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A341" s="5" t="s">
         <v>1499</v>
       </c>
@@ -15709,7 +15705,7 @@
         <v>1501</v>
       </c>
     </row>
-    <row r="342" spans="1:9" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:9" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A342" s="5" t="s">
         <v>1502</v>
       </c>
@@ -15738,7 +15734,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="343" spans="1:9" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:9" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A343" s="5" t="s">
         <v>1506</v>
       </c>
@@ -15767,7 +15763,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="344" spans="1:9" ht="264" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:9" ht="255" x14ac:dyDescent="0.2">
       <c r="A344" s="5" t="s">
         <v>1510</v>
       </c>
@@ -15792,7 +15788,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="345" spans="1:9" ht="211.2" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:9" ht="204" x14ac:dyDescent="0.2">
       <c r="A345" s="5" t="s">
         <v>1514</v>
       </c>
@@ -15817,7 +15813,7 @@
         <v>1517</v>
       </c>
     </row>
-    <row r="346" spans="1:9" ht="145.19999999999999" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:9" ht="153" x14ac:dyDescent="0.2">
       <c r="A346" s="5" t="s">
         <v>1518</v>
       </c>
@@ -15842,7 +15838,7 @@
         <v>1521</v>
       </c>
     </row>
-    <row r="347" spans="1:9" ht="171.6" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:9" ht="165.75" x14ac:dyDescent="0.2">
       <c r="A347" s="5" t="s">
         <v>1522</v>
       </c>
@@ -15867,7 +15863,7 @@
         <v>1525</v>
       </c>
     </row>
-    <row r="348" spans="1:9" ht="224.4" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:9" ht="216.75" x14ac:dyDescent="0.2">
       <c r="A348" s="5" t="s">
         <v>1526</v>
       </c>
@@ -15896,7 +15892,7 @@
         <v>1529</v>
       </c>
     </row>
-    <row r="349" spans="1:9" ht="92.4" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:9" ht="102" x14ac:dyDescent="0.2">
       <c r="A349" s="5" t="s">
         <v>1530</v>
       </c>
@@ -15925,7 +15921,7 @@
         <v>1533</v>
       </c>
     </row>
-    <row r="350" spans="1:9" ht="171.6" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:9" ht="165.75" x14ac:dyDescent="0.2">
       <c r="A350" s="5" t="s">
         <v>1534</v>
       </c>
@@ -15950,7 +15946,7 @@
         <v>1537</v>
       </c>
     </row>
-    <row r="351" spans="1:9" ht="66" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:9" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A351" s="5" t="s">
         <v>1538</v>
       </c>
@@ -15975,7 +15971,7 @@
         <v>1541</v>
       </c>
     </row>
-    <row r="352" spans="1:9" ht="145.19999999999999" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:9" ht="140.25" x14ac:dyDescent="0.2">
       <c r="A352" s="5" t="s">
         <v>1542</v>
       </c>
@@ -16000,7 +15996,7 @@
         <v>1545</v>
       </c>
     </row>
-    <row r="353" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:9" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A353" s="5" t="s">
         <v>1546</v>
       </c>
@@ -16025,7 +16021,7 @@
         <v>1549</v>
       </c>
     </row>
-    <row r="354" spans="1:9" ht="145.19999999999999" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:9" ht="140.25" x14ac:dyDescent="0.2">
       <c r="A354" s="5" t="s">
         <v>1550</v>
       </c>
@@ -16050,7 +16046,7 @@
         <v>1553</v>
       </c>
     </row>
-    <row r="355" spans="1:9" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:9" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A355" s="5" t="s">
         <v>1554</v>
       </c>
@@ -16075,7 +16071,7 @@
         <v>1556</v>
       </c>
     </row>
-    <row r="356" spans="1:9" ht="198" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:9" ht="191.25" x14ac:dyDescent="0.2">
       <c r="A356" s="5" t="s">
         <v>1557</v>
       </c>
@@ -16104,7 +16100,7 @@
         <v>1560</v>
       </c>
     </row>
-    <row r="357" spans="1:9" ht="184.8" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:9" ht="191.25" x14ac:dyDescent="0.2">
       <c r="A357" s="5" t="s">
         <v>1561</v>
       </c>
@@ -16129,7 +16125,7 @@
         <v>1564</v>
       </c>
     </row>
-    <row r="358" spans="1:9" ht="105.6" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:9" ht="102" x14ac:dyDescent="0.2">
       <c r="A358" s="5" t="s">
         <v>1565</v>
       </c>
@@ -16154,7 +16150,7 @@
         <v>1567</v>
       </c>
     </row>
-    <row r="359" spans="1:9" ht="290.39999999999998" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:9" ht="280.5" x14ac:dyDescent="0.2">
       <c r="A359" s="5" t="s">
         <v>1568</v>
       </c>
@@ -16179,7 +16175,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="360" spans="1:9" ht="132" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:9" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A360" s="5" t="s">
         <v>1571</v>
       </c>
@@ -16204,7 +16200,7 @@
         <v>1573</v>
       </c>
     </row>
-    <row r="361" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:9" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A361" s="5" t="s">
         <v>1574</v>
       </c>
@@ -16229,7 +16225,7 @@
         <v>1577</v>
       </c>
     </row>
-    <row r="362" spans="1:9" ht="66" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:9" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A362" s="5" t="s">
         <v>1578</v>
       </c>
@@ -16258,7 +16254,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="363" spans="1:9" ht="92.4" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:9" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A363" s="5" t="s">
         <v>1582</v>
       </c>
@@ -16287,7 +16283,7 @@
         <v>1585</v>
       </c>
     </row>
-    <row r="364" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A364" s="5" t="s">
         <v>1586</v>
       </c>
@@ -16316,7 +16312,7 @@
         <v>1589</v>
       </c>
     </row>
-    <row r="365" spans="1:9" ht="224.4" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:9" ht="229.5" x14ac:dyDescent="0.2">
       <c r="A365" s="5" t="s">
         <v>1590</v>
       </c>
@@ -16341,7 +16337,7 @@
         <v>1593</v>
       </c>
     </row>
-    <row r="366" spans="1:9" ht="198" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:9" ht="204" x14ac:dyDescent="0.2">
       <c r="A366" s="5" t="s">
         <v>1594</v>
       </c>
@@ -16366,7 +16362,7 @@
         <v>1597</v>
       </c>
     </row>
-    <row r="367" spans="1:9" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A367" s="5" t="s">
         <v>1598</v>
       </c>
@@ -16391,7 +16387,7 @@
         <v>1601</v>
       </c>
     </row>
-    <row r="368" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:9" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A368" s="5" t="s">
         <v>1602</v>
       </c>
@@ -16416,7 +16412,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="369" spans="1:9" ht="184.8" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:9" ht="178.5" x14ac:dyDescent="0.2">
       <c r="A369" s="5" t="s">
         <v>1608</v>
       </c>
@@ -16441,7 +16437,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="370" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:9" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A370" s="5" t="s">
         <v>1613</v>
       </c>
@@ -16470,7 +16466,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="371" spans="1:9" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A371" s="5" t="s">
         <v>1618</v>
       </c>
@@ -16499,7 +16495,7 @@
         <v>1622</v>
       </c>
     </row>
-    <row r="372" spans="1:9" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:9" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A372" s="5" t="s">
         <v>1623</v>
       </c>
@@ -16524,7 +16520,7 @@
         <v>1626</v>
       </c>
     </row>
-    <row r="373" spans="1:9" ht="105.6" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:9" ht="102" x14ac:dyDescent="0.2">
       <c r="A373" s="5" t="s">
         <v>1627</v>
       </c>
@@ -16549,7 +16545,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="374" spans="1:9" ht="92.4" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:9" ht="102" x14ac:dyDescent="0.2">
       <c r="A374" s="5" t="s">
         <v>1632</v>
       </c>
@@ -16578,7 +16574,7 @@
         <v>1637</v>
       </c>
     </row>
-    <row r="375" spans="1:9" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A375" s="5" t="s">
         <v>1638</v>
       </c>
@@ -16603,7 +16599,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="376" spans="1:9" ht="66" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:9" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A376" s="5" t="s">
         <v>1643</v>
       </c>
@@ -16628,7 +16624,7 @@
         <v>1648</v>
       </c>
     </row>
-    <row r="377" spans="1:9" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:9" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A377" s="5" t="s">
         <v>1649</v>
       </c>
@@ -16657,7 +16653,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="378" spans="1:9" ht="66" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:9" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A378" s="5" t="s">
         <v>1655</v>
       </c>
@@ -16682,7 +16678,7 @@
         <v>1660</v>
       </c>
     </row>
-    <row r="379" spans="1:9" ht="158.4" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:9" ht="153" x14ac:dyDescent="0.2">
       <c r="A379" s="5" t="s">
         <v>1661</v>
       </c>
@@ -16711,7 +16707,7 @@
         <v>1665</v>
       </c>
     </row>
-    <row r="380" spans="1:9" ht="66" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:9" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A380" s="5" t="s">
         <v>1666</v>
       </c>
@@ -16736,7 +16732,7 @@
         <v>1670</v>
       </c>
     </row>
-    <row r="381" spans="1:9" ht="158.4" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:9" ht="153" x14ac:dyDescent="0.2">
       <c r="A381" s="5" t="s">
         <v>1671</v>
       </c>
@@ -16765,7 +16761,7 @@
         <v>1675</v>
       </c>
     </row>
-    <row r="382" spans="1:9" ht="132" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:9" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A382" s="5" t="s">
         <v>1676</v>
       </c>
@@ -16790,7 +16786,7 @@
         <v>1679</v>
       </c>
     </row>
-    <row r="383" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:9" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A383" s="5" t="s">
         <v>1680</v>
       </c>
@@ -16819,7 +16815,7 @@
         <v>1683</v>
       </c>
     </row>
-    <row r="384" spans="1:9" ht="92.4" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:9" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A384" s="5" t="s">
         <v>1684</v>
       </c>
@@ -16844,7 +16840,7 @@
         <v>1688</v>
       </c>
     </row>
-    <row r="385" spans="1:9" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A385" s="5" t="s">
         <v>1689</v>
       </c>
@@ -16869,7 +16865,7 @@
         <v>1692</v>
       </c>
     </row>
-    <row r="386" spans="1:9" ht="105.6" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:9" ht="102" x14ac:dyDescent="0.2">
       <c r="A386" s="5" t="s">
         <v>1693</v>
       </c>
@@ -16894,7 +16890,7 @@
         <v>1696</v>
       </c>
     </row>
-    <row r="387" spans="1:9" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:9" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A387" s="5" t="s">
         <v>1697</v>
       </c>
@@ -16923,7 +16919,7 @@
         <v>1701</v>
       </c>
     </row>
-    <row r="388" spans="1:9" ht="132" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:9" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A388" s="5" t="s">
         <v>1702</v>
       </c>
@@ -16948,7 +16944,7 @@
         <v>1707</v>
       </c>
     </row>
-    <row r="389" spans="1:9" ht="145.19999999999999" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:9" ht="140.25" x14ac:dyDescent="0.2">
       <c r="A389" s="5" t="s">
         <v>1708</v>
       </c>
@@ -16977,7 +16973,7 @@
         <v>1712</v>
       </c>
     </row>
-    <row r="390" spans="1:9" ht="211.2" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:9" ht="216.75" x14ac:dyDescent="0.2">
       <c r="A390" s="5" t="s">
         <v>1713</v>
       </c>
@@ -17002,7 +16998,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="391" spans="1:9" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:9" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A391" s="5" t="s">
         <v>1718</v>
       </c>
@@ -17027,7 +17023,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="392" spans="1:9" ht="105.6" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:9" ht="102" x14ac:dyDescent="0.2">
       <c r="A392" s="5" t="s">
         <v>1723</v>
       </c>
@@ -17056,7 +17052,7 @@
         <v>1726</v>
       </c>
     </row>
-    <row r="393" spans="1:9" ht="92.4" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:9" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A393" s="5" t="s">
         <v>1727</v>
       </c>
@@ -17085,7 +17081,7 @@
         <v>1729</v>
       </c>
     </row>
-    <row r="394" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:9" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A394" s="5" t="s">
         <v>1730</v>
       </c>
@@ -17110,7 +17106,7 @@
         <v>1734</v>
       </c>
     </row>
-    <row r="395" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:9" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A395" s="5" t="s">
         <v>1735</v>
       </c>
@@ -17135,7 +17131,7 @@
         <v>1739</v>
       </c>
     </row>
-    <row r="396" spans="1:9" ht="92.4" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:9" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A396" s="5" t="s">
         <v>1740</v>
       </c>
@@ -17164,7 +17160,7 @@
         <v>1745</v>
       </c>
     </row>
-    <row r="397" spans="1:9" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:9" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A397" s="5" t="s">
         <v>1746</v>
       </c>
@@ -17189,7 +17185,7 @@
         <v>1751</v>
       </c>
     </row>
-    <row r="398" spans="1:9" ht="145.19999999999999" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:9" ht="140.25" x14ac:dyDescent="0.2">
       <c r="A398" s="5" t="s">
         <v>1752</v>
       </c>
@@ -17214,7 +17210,7 @@
         <v>1756</v>
       </c>
     </row>
-    <row r="399" spans="1:9" ht="145.19999999999999" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:9" ht="140.25" x14ac:dyDescent="0.2">
       <c r="A399" s="5" t="s">
         <v>1757</v>
       </c>
@@ -17239,7 +17235,7 @@
         <v>1761</v>
       </c>
     </row>
-    <row r="400" spans="1:9" ht="132" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:9" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A400" s="5" t="s">
         <v>1762</v>
       </c>
@@ -17268,7 +17264,7 @@
         <v>1765</v>
       </c>
     </row>
-    <row r="401" spans="1:9" ht="105.6" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:9" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A401" s="5" t="s">
         <v>1766</v>
       </c>
@@ -17297,7 +17293,7 @@
         <v>1769</v>
       </c>
     </row>
-    <row r="402" spans="1:9" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:9" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A402" s="5" t="s">
         <v>1770</v>
       </c>
@@ -17326,7 +17322,7 @@
         <v>1774</v>
       </c>
     </row>
-    <row r="403" spans="1:9" ht="66" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:9" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A403" s="5" t="s">
         <v>1775</v>
       </c>
@@ -17351,7 +17347,7 @@
         <v>1778</v>
       </c>
     </row>
-    <row r="405" spans="1:9" ht="12.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:9" ht="12.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F405" s="22" t="s">
         <v>1779</v>
       </c>
@@ -17364,7 +17360,7 @@
         <v>197450000</v>
       </c>
     </row>
-    <row r="406" spans="1:9" ht="12.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:9" ht="12.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F406" s="22" t="s">
         <v>1780</v>
       </c>
@@ -17377,7 +17373,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="407" spans="1:9" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:9" ht="25.9" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F407" s="8" t="s">
         <v>1781</v>
       </c>
@@ -17390,7 +17386,7 @@
         <v>197450000</v>
       </c>
     </row>
-    <row r="408" spans="1:9" ht="12.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:9" ht="12.95" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F408" s="10" t="s">
         <v>1782</v>
       </c>
@@ -17414,6 +17410,24 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100420F3B8DD6992F4B9C1DE9DD96E4486F" ma:contentTypeVersion="2" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7ad8ec248fe312b9dc894641bff4c9fd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="bfdc0969-8447-451b-99af-f83fc3c713f3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6a8c71706f1c6f62e424fe97951f1408" ns1:_="" ns2:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -17570,25 +17584,25 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1E4B311-B025-4059-AEA1-54B85DF05237}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{49E6454E-F88B-4D0C-BF85-B47F5C2AA983}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00359983-A2E7-417D-8502-75ED7ADB7738}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -17605,22 +17619,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{49E6454E-F88B-4D0C-BF85-B47F5C2AA983}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1E4B311-B025-4059-AEA1-54B85DF05237}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>